--- a/pipeline/credit_rating/output/fiinratings_xhtn_20260920.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20260920.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -632,7 +632,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -770,7 +770,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-09-20 08:47:39</t>
+          <t>2026-09-20 13:11:30</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
